--- a/data/trans_camb/P26-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P26-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,99</t>
+          <t>-5,14; 4,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,38</t>
+          <t>-7,75; 2,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,89; -14,4</t>
+          <t>-23,82; -14,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 5,84</t>
+          <t>-5,36; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -4,84</t>
+          <t>-15,13; -5,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -24,05</t>
+          <t>-32,24; -23,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,79</t>
+          <t>-3,52; 3,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -2,67</t>
+          <t>-9,88; -2,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,07; -20,46</t>
+          <t>-27,13; -20,48</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 20,01</t>
+          <t>-17,22; 18,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 9,55</t>
+          <t>-24,92; 8,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -54,28</t>
+          <t>-78,19; -54,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 16,82</t>
+          <t>-13,35; 17,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,89; -13,88</t>
+          <t>-38,47; -15,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,79; -68,74</t>
+          <t>-80,24; -69,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 12,66</t>
+          <t>-10,23; 11,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,69; -8,8</t>
+          <t>-28,95; -8,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,67; -65,62</t>
+          <t>-78,06; -65,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 8,06</t>
+          <t>-0,73; 8,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -1,25</t>
+          <t>-9,39; -1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 32,02</t>
+          <t>-20,75; 38,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 6,89</t>
+          <t>-2,88; 6,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,92; -7,88</t>
+          <t>-17,11; -8,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,57; -19,57</t>
+          <t>-27,61; -19,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,41</t>
+          <t>-0,03; 6,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; -5,58</t>
+          <t>-11,71; -5,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 19,11</t>
+          <t>-22,33; 16,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 30,88</t>
+          <t>-2,38; 31,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,04; -4,65</t>
+          <t>-30,29; -3,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 116,29</t>
+          <t>-70,7; 144,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 19,7</t>
+          <t>-6,94; 19,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,5; -22,16</t>
+          <t>-42,48; -24,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,07; -54,95</t>
+          <t>-68,34; -54,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 20,53</t>
+          <t>-0,09; 19,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,57; -17,63</t>
+          <t>-34,0; -18,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 57,88</t>
+          <t>-66,45; 52,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,56</t>
+          <t>-2,57; 7,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 4,41</t>
+          <t>-6,6; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -12,62</t>
+          <t>-22,53; -12,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 10,77</t>
+          <t>-0,48; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,3</t>
+          <t>-6,49; 3,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,02; -18,34</t>
+          <t>-31,91; -17,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 8,27</t>
+          <t>0,85; 8,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,13</t>
+          <t>-4,7; 2,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,5; -16,41</t>
+          <t>-26,11; -16,88</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 32,0</t>
+          <t>-7,63; 29,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 17,31</t>
+          <t>-20,58; 13,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -45,32</t>
+          <t>-69,49; -45,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 32,87</t>
+          <t>-1,21; 31,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 12,4</t>
+          <t>-17,04; 11,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,8; -52,15</t>
+          <t>-83,52; -50,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 26,9</t>
+          <t>2,48; 27,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 6,96</t>
+          <t>-13,69; 7,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,66; -51,97</t>
+          <t>-77,31; -53,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,5</t>
+          <t>4,93; 13,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,64</t>
+          <t>-7,53; 1,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -8,12</t>
+          <t>-16,49; -7,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,91</t>
+          <t>-5,15; 3,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -10,89</t>
+          <t>-19,55; -10,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,68; -18,84</t>
+          <t>-27,09; -18,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,78</t>
+          <t>0,76; 6,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,73; -7,02</t>
+          <t>-12,6; -6,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -14,92</t>
+          <t>-20,8; -14,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,81; 52,02</t>
+          <t>16,27; 53,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 2,71</t>
+          <t>-24,78; 5,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,93; -30,56</t>
+          <t>-54,86; -30,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 11,37</t>
+          <t>-12,74; 11,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,02; -30,92</t>
+          <t>-49,93; -31,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,67; -53,94</t>
+          <t>-70,16; -53,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 21,73</t>
+          <t>2,18; 22,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,23; -22,26</t>
+          <t>-37,09; -22,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,67; -47,59</t>
+          <t>-61,77; -48,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,67</t>
+          <t>1,84; 6,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,96</t>
+          <t>-5,73; -1,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 10,12</t>
+          <t>-17,5; 7,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,14</t>
+          <t>-0,96; 4,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -8,17</t>
+          <t>-12,63; -7,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,88; -21,91</t>
+          <t>-27,27; -21,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,59</t>
+          <t>1,25; 4,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -5,36</t>
+          <t>-8,51; -5,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -6,08</t>
+          <t>-21,23; -6,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,98; 24,33</t>
+          <t>6,17; 23,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -3,51</t>
+          <t>-19,14; -4,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 35,66</t>
+          <t>-60,93; 25,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 11,53</t>
+          <t>-2,52; 11,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -22,59</t>
+          <t>-32,98; -22,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -61,01</t>
+          <t>-72,0; -60,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,43</t>
+          <t>3,62; 14,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,33; -16,61</t>
+          <t>-25,31; -16,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -18,62</t>
+          <t>-63,98; -19,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P26-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P26-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-19,48</t>
+          <t>-19,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-28,24</t>
+          <t>-28,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-23,78</t>
+          <t>-23,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 4,6</t>
+          <t>-5,42; 4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,1</t>
+          <t>-7,87; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,82; -14,37</t>
+          <t>-23,93; -14,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 6,06</t>
+          <t>-4,86; 6,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -5,43</t>
+          <t>-15,11; -5,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,24; -23,95</t>
+          <t>-32,51; -23,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,69</t>
+          <t>-4,1; 3,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -2,55</t>
+          <t>-10,17; -2,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,13; -20,48</t>
+          <t>-26,96; -20,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-68,97%</t>
+          <t>-69,12%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-75,43%</t>
+          <t>-75,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-72,57%</t>
+          <t>-72,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 18,6</t>
+          <t>-17,75; 16,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 8,59</t>
+          <t>-25,08; 8,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,19; -54,38</t>
+          <t>-77,96; -56,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 17,15</t>
+          <t>-12,19; 17,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,47; -15,5</t>
+          <t>-37,81; -14,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,24; -69,11</t>
+          <t>-80,74; -68,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 11,71</t>
+          <t>-11,74; 10,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -8,48</t>
+          <t>-29,3; -9,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,06; -65,58</t>
+          <t>-77,58; -66,58</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>-19,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-23,34</t>
+          <t>-23,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,54</t>
+          <t>-21,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 8,3</t>
+          <t>-0,14; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,39; -1,03</t>
+          <t>-9,52; -0,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 38,46</t>
+          <t>-23,29; -15,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 6,75</t>
+          <t>-2,06; 7,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; -8,65</t>
+          <t>-17,11; -8,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,61; -19,55</t>
+          <t>-27,08; -19,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,23</t>
+          <t>-0,43; 6,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,71; -5,73</t>
+          <t>-11,74; -5,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 16,79</t>
+          <t>-24,14; -18,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>-67,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-61,95%</t>
+          <t>-62,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,74%</t>
+          <t>-64,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 31,11</t>
+          <t>-0,43; 32,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,29; -3,62</t>
+          <t>-30,59; -2,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 144,59</t>
+          <t>-75,47; -57,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 19,34</t>
+          <t>-5,19; 20,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,48; -24,24</t>
+          <t>-42,85; -22,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,34; -54,86</t>
+          <t>-68,13; -55,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 19,96</t>
+          <t>-1,44; 20,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,0; -18,03</t>
+          <t>-33,47; -17,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,45; 52,91</t>
+          <t>-69,54; -59,12</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-17,61</t>
+          <t>-18,26</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-23,45</t>
+          <t>-19,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-20,48</t>
+          <t>-19,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,95</t>
+          <t>-2,13; 8,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 3,73</t>
+          <t>-6,52; 3,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -12,6</t>
+          <t>-22,9; -13,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 10,48</t>
+          <t>-0,42; 10,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 3,77</t>
+          <t>-6,76; 4,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,91; -17,25</t>
+          <t>-24,74; -15,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,26</t>
+          <t>0,75; 8,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 2,22</t>
+          <t>-4,87; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -16,88</t>
+          <t>-22,33; -15,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-59,21%</t>
+          <t>-61,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-65,25%</t>
+          <t>-55,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-62,4%</t>
+          <t>-58,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 29,24</t>
+          <t>-6,31; 30,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 13,96</t>
+          <t>-20,25; 13,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,49; -45,07</t>
+          <t>-71,53; -48,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 31,51</t>
+          <t>-1,0; 32,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 11,36</t>
+          <t>-17,48; 12,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,52; -50,68</t>
+          <t>-63,75; -45,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 27,36</t>
+          <t>2,19; 26,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 7,23</t>
+          <t>-14,02; 7,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,31; -53,28</t>
+          <t>-64,65; -49,85</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,25</t>
+          <t>-12,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-22,89</t>
+          <t>-22,38</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-17,85</t>
+          <t>-17,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,54</t>
+          <t>3,94; 13,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,36</t>
+          <t>-7,86; 0,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,49; -7,87</t>
+          <t>-16,45; -8,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,88</t>
+          <t>-5,22; 3,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,55; -10,74</t>
+          <t>-19,18; -11,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,09; -18,72</t>
+          <t>-26,07; -18,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,99</t>
+          <t>0,96; 7,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -6,93</t>
+          <t>-12,38; -6,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,8; -14,87</t>
+          <t>-20,31; -14,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-43,88%</t>
+          <t>-44,45%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-61,76%</t>
+          <t>-60,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-54,58%</t>
+          <t>-53,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,27; 53,43</t>
+          <t>12,15; 49,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 5,43</t>
+          <t>-26,58; 1,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,86; -30,21</t>
+          <t>-54,73; -31,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 11,35</t>
+          <t>-13,54; 10,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,93; -31,19</t>
+          <t>-48,69; -31,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,16; -53,66</t>
+          <t>-66,41; -53,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 22,14</t>
+          <t>2,78; 23,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,09; -22,21</t>
+          <t>-36,45; -20,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,77; -48,13</t>
+          <t>-59,67; -47,53</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-10,14</t>
+          <t>-17,18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-24,21</t>
+          <t>-23,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-17,28</t>
+          <t>-20,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,53</t>
+          <t>1,96; 6,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,16</t>
+          <t>-5,51; -1,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 7,46</t>
+          <t>-19,49; -15,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,22</t>
+          <t>-1,06; 3,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -7,91</t>
+          <t>-12,87; -8,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,27; -21,99</t>
+          <t>-25,49; -21,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,77</t>
+          <t>1,24; 4,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -5,23</t>
+          <t>-8,42; -5,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-21,23; -6,26</t>
+          <t>-21,65; -18,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-35,41%</t>
+          <t>-60,0%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-65,27%</t>
+          <t>-63,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-52,56%</t>
+          <t>-61,63%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,17; 23,85</t>
+          <t>6,5; 23,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -4,44</t>
+          <t>-18,62; -3,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 25,05</t>
+          <t>-65,17; -54,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,97</t>
+          <t>-2,72; 10,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,98; -22,4</t>
+          <t>-33,48; -22,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-72,0; -60,76</t>
+          <t>-66,3; -59,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,87</t>
+          <t>3,76; 14,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -16,4</t>
+          <t>-25,02; -15,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -19,64</t>
+          <t>-64,36; -58,43</t>
         </is>
       </c>
     </row>
